--- a/data/ground_truth/CPIN.xlsx
+++ b/data/ground_truth/CPIN.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/muhammadnajmirahmani/Belajar/ProjectDatasaur/data/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F4C128-3C73-8544-BB9F-71C569BDF92E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD0A913-2B62-D143-8B15-C3B28076C4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29300" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
-    <sheet name="lokasi kebun" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="lokasi kebun" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,22 +30,175 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="c1H/Q4ZdR4yLnEJr0IZqFh3FObkfqorOjDyrNKq9VL8="/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="71">
+  <si>
+    <t>(HANYA YANG BISA DIATRIBUSIKAN KE ENTITAS INDUK SAJA)</t>
+  </si>
+  <si>
+    <t>CPIN</t>
+  </si>
+  <si>
+    <t>DINYATAKAN DALAM RUPIAH</t>
+  </si>
+  <si>
+    <t>kecuali nilai nominal dan data saham</t>
+  </si>
+  <si>
+    <t>Q2 2026</t>
+  </si>
+  <si>
+    <t>Q1 2026</t>
+  </si>
+  <si>
+    <t>Q4 2025</t>
+  </si>
+  <si>
+    <t>Q3 2025</t>
+  </si>
+  <si>
+    <t>Q2 2025</t>
+  </si>
+  <si>
+    <t>Q1 2025</t>
+  </si>
+  <si>
+    <t>TAHUNAN 2024</t>
+  </si>
+  <si>
+    <t>Q3 2024</t>
+  </si>
+  <si>
+    <t>Q2 2024</t>
+  </si>
+  <si>
+    <t>Q1 2024</t>
+  </si>
+  <si>
+    <t>TAHUNAN 2023</t>
+  </si>
+  <si>
+    <t>Q3 2023</t>
+  </si>
+  <si>
+    <t>Q2 2023</t>
+  </si>
+  <si>
+    <t>Q1 2023</t>
+  </si>
+  <si>
+    <t>TAHUNAN 2022</t>
+  </si>
+  <si>
+    <t>Q3 2022</t>
+  </si>
+  <si>
+    <t>Q2 2022</t>
+  </si>
+  <si>
+    <t>Q1 2022</t>
+  </si>
+  <si>
+    <t>TAHUNAN 2021</t>
+  </si>
+  <si>
+    <t>Q3 2021</t>
+  </si>
+  <si>
+    <t>Q2 2021</t>
+  </si>
+  <si>
+    <t>Q1 2021</t>
+  </si>
+  <si>
+    <t>TAHUNAN 2020</t>
+  </si>
+  <si>
+    <t>Q3 2020</t>
+  </si>
+  <si>
+    <t>Q2 2020</t>
+  </si>
+  <si>
+    <t>Q1 2020</t>
+  </si>
+  <si>
+    <t>Aset</t>
+  </si>
+  <si>
+    <t>total aset lancar</t>
+  </si>
+  <si>
+    <t>KAS</t>
+  </si>
+  <si>
+    <t>liabilitas</t>
+  </si>
+  <si>
+    <t>Utang Bank SAJA Jangka Pendek + Panjang jatuh tempo</t>
+  </si>
+  <si>
+    <t>ekuitas</t>
+  </si>
+  <si>
+    <t>laba bersih</t>
+  </si>
+  <si>
+    <t>pendapatan dari kontrak dengan pelanggan</t>
+  </si>
+  <si>
+    <t>kas dari aktivitas operasi</t>
+  </si>
+  <si>
+    <t>total share</t>
+  </si>
+  <si>
+    <t>Harga saham rupiah</t>
+  </si>
+  <si>
+    <t>Book Value per share</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>ROA</t>
+  </si>
+  <si>
+    <t>ROE</t>
+  </si>
+  <si>
+    <t>PBV</t>
+  </si>
+  <si>
+    <t>PE</t>
+  </si>
+  <si>
+    <t>EPS</t>
+  </si>
+  <si>
+    <t>DER</t>
+  </si>
+  <si>
+    <t>Kurs</t>
+  </si>
+  <si>
+    <t>USD to IDR</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Converted</t>
+  </si>
   <si>
     <t>Perusahaan</t>
   </si>
   <si>
-    <t>(HANYA YANG BISA DIATRIBUSIKAN KE ENTITAS INDUK SAJA)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lokasi </t>
   </si>
   <si>
@@ -95,165 +248,6 @@
   </si>
   <si>
     <t>Tanjung Buyu Perkasa Plantation</t>
-  </si>
-  <si>
-    <t>DINYATAKAN DALAM RUPIAH</t>
-  </si>
-  <si>
-    <t>kecuali nilai nominal dan data saham</t>
-  </si>
-  <si>
-    <t>Q2 2026</t>
-  </si>
-  <si>
-    <t>Q1 2026</t>
-  </si>
-  <si>
-    <t>Q4 2025</t>
-  </si>
-  <si>
-    <t>Q3 2025</t>
-  </si>
-  <si>
-    <t>Q2 2025</t>
-  </si>
-  <si>
-    <t>Q1 2025</t>
-  </si>
-  <si>
-    <t>TAHUNAN 2024</t>
-  </si>
-  <si>
-    <t>Q3 2024</t>
-  </si>
-  <si>
-    <t>Q2 2024</t>
-  </si>
-  <si>
-    <t>Q1 2024</t>
-  </si>
-  <si>
-    <t>TAHUNAN 2023</t>
-  </si>
-  <si>
-    <t>Q3 2023</t>
-  </si>
-  <si>
-    <t>Q2 2023</t>
-  </si>
-  <si>
-    <t>Q1 2023</t>
-  </si>
-  <si>
-    <t>TAHUNAN 2022</t>
-  </si>
-  <si>
-    <t>Q3 2022</t>
-  </si>
-  <si>
-    <t>Q2 2022</t>
-  </si>
-  <si>
-    <t>Q1 2022</t>
-  </si>
-  <si>
-    <t>TAHUNAN 2021</t>
-  </si>
-  <si>
-    <t>Q3 2021</t>
-  </si>
-  <si>
-    <t>Q2 2021</t>
-  </si>
-  <si>
-    <t>Q1 2021</t>
-  </si>
-  <si>
-    <t>TAHUNAN 2020</t>
-  </si>
-  <si>
-    <t>Q3 2020</t>
-  </si>
-  <si>
-    <t>Q2 2020</t>
-  </si>
-  <si>
-    <t>Q1 2020</t>
-  </si>
-  <si>
-    <t>Aset</t>
-  </si>
-  <si>
-    <t>total aset lancar</t>
-  </si>
-  <si>
-    <t>KAS</t>
-  </si>
-  <si>
-    <t>liabilitas</t>
-  </si>
-  <si>
-    <t>Utang Bank SAJA Jangka Pendek + Panjang jatuh tempo</t>
-  </si>
-  <si>
-    <t>ekuitas</t>
-  </si>
-  <si>
-    <t>laba bersih</t>
-  </si>
-  <si>
-    <t>pendapatan dari kontrak dengan pelanggan</t>
-  </si>
-  <si>
-    <t>kas dari aktivitas operasi</t>
-  </si>
-  <si>
-    <t>total share</t>
-  </si>
-  <si>
-    <t>Harga saham rupiah</t>
-  </si>
-  <si>
-    <t>Book Value per share</t>
-  </si>
-  <si>
-    <t>P1</t>
-  </si>
-  <si>
-    <t>ROA</t>
-  </si>
-  <si>
-    <t>ROE</t>
-  </si>
-  <si>
-    <t>PBV</t>
-  </si>
-  <si>
-    <t>PE</t>
-  </si>
-  <si>
-    <t>EPS</t>
-  </si>
-  <si>
-    <t>DER</t>
-  </si>
-  <si>
-    <t>Kurs</t>
-  </si>
-  <si>
-    <t>USD to IDR</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Converted</t>
-  </si>
-  <si>
-    <t>CPIN</t>
-  </si>
-  <si>
-    <t>16398000000.0</t>
   </si>
 </sst>
 </file>
@@ -335,7 +329,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -607,10 +601,10 @@
   <sheetData>
     <row r="1" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>1</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>70</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -637,12 +631,12 @@
     </row>
     <row r="2" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -668,87 +662,87 @@
     <row r="3" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="S3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="T3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="U3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="V3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="W3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="X3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="Y3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="Z3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="AA3" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="S3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="T3" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="U3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="V3" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="W3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="X3" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" s="6" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="B4" s="18">
         <v>52380933000000</v>
@@ -815,7 +809,7 @@
     </row>
     <row r="5" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="B5" s="18">
         <v>30932743000000</v>
@@ -882,7 +876,7 @@
     </row>
     <row r="6" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B6" s="18">
         <v>5368132000000</v>
@@ -949,7 +943,7 @@
     </row>
     <row r="7" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B7" s="18">
         <v>17469626000000</v>
@@ -1016,7 +1010,7 @@
     </row>
     <row r="8" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="B8" s="18">
         <v>4832090000000</v>
@@ -1083,7 +1077,7 @@
     </row>
     <row r="9" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B9" s="18">
         <v>34897180000000</v>
@@ -1150,7 +1144,7 @@
     </row>
     <row r="10" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B10" s="18">
         <v>3708330000000</v>
@@ -1217,7 +1211,7 @@
     </row>
     <row r="11" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="B11" s="18">
         <v>39418494000000</v>
@@ -1284,7 +1278,7 @@
     </row>
     <row r="12" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B12" s="18">
         <v>1726556000000</v>
@@ -1351,7 +1345,7 @@
     </row>
     <row r="13" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B13" s="18">
         <v>16398000000</v>
@@ -1418,72 +1412,90 @@
     </row>
     <row r="14" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
+        <v>40</v>
+      </c>
+      <c r="B14" s="4">
+        <v>3070</v>
+      </c>
+      <c r="C14" s="4">
+        <v>3350</v>
+      </c>
+      <c r="D14" s="4">
+        <v>4160</v>
+      </c>
+      <c r="E14" s="4">
+        <v>4610</v>
+      </c>
+      <c r="F14" s="4">
+        <v>4440</v>
+      </c>
+      <c r="G14" s="4">
+        <v>4860</v>
+      </c>
+      <c r="H14" s="5">
+        <v>4930</v>
+      </c>
+      <c r="I14" s="5">
+        <v>4790</v>
+      </c>
+      <c r="J14" s="5">
+        <v>5150</v>
+      </c>
       <c r="K14" s="5">
-        <v>444</v>
+        <v>4900</v>
       </c>
       <c r="L14" s="5">
-        <v>448</v>
+        <v>5275</v>
       </c>
       <c r="M14" s="5">
-        <v>454</v>
+        <v>5500</v>
       </c>
       <c r="N14" s="5">
-        <v>458</v>
+        <v>5275</v>
       </c>
       <c r="O14" s="5">
-        <v>454</v>
+        <v>5200</v>
       </c>
       <c r="P14" s="5">
-        <v>468</v>
+        <v>5000</v>
       </c>
       <c r="Q14" s="5">
-        <v>580</v>
+        <v>5750</v>
       </c>
       <c r="R14" s="5">
-        <v>610</v>
+        <v>5700</v>
       </c>
       <c r="S14" s="5">
-        <v>352</v>
+        <v>5025</v>
       </c>
       <c r="T14" s="5">
-        <v>725</v>
+        <v>4930</v>
       </c>
       <c r="U14" s="7">
-        <v>570</v>
+        <v>6000</v>
       </c>
       <c r="V14" s="7">
-        <v>570</v>
+        <v>6325</v>
       </c>
       <c r="W14" s="4">
-        <v>570</v>
+        <v>6400</v>
       </c>
       <c r="X14" s="7">
-        <v>570</v>
+        <v>6400</v>
       </c>
       <c r="Y14" s="7">
-        <v>570</v>
+        <v>6700</v>
       </c>
       <c r="Z14" s="7">
-        <v>1140</v>
+        <v>6250</v>
       </c>
       <c r="AA14" s="7">
-        <v>1140</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="B15" s="6">
         <f t="shared" ref="B15:AA15" si="0">B9/B13</f>
@@ -1554,7 +1566,7 @@
         <v>1571.9768874252957</v>
       </c>
       <c r="S15" s="6">
-        <f>S9/S13</f>
+        <f t="shared" si="0"/>
         <v>1605.4734113916331</v>
       </c>
       <c r="T15" s="6" t="e">
@@ -1592,7 +1604,7 @@
     </row>
     <row r="16" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="B16" s="6">
         <f t="shared" ref="B16:AA16" si="1">B5-B7</f>
@@ -1663,7 +1675,7 @@
         <v>5382636000000</v>
       </c>
       <c r="S16" s="6">
-        <f>S5-S7</f>
+        <f t="shared" si="1"/>
         <v>6191565000000</v>
       </c>
       <c r="T16" s="6">
@@ -1701,7 +1713,7 @@
     </row>
     <row r="17" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="B17" s="10">
         <f t="shared" ref="B17:AA17" si="2">B10/B4</f>
@@ -1810,7 +1822,7 @@
     </row>
     <row r="18" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="B18" s="10">
         <f t="shared" ref="B18:AA18" si="3">B10/B9</f>
@@ -1919,79 +1931,79 @@
     </row>
     <row r="19" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B19" s="11">
         <f t="shared" ref="B19:AA19" si="4">B14/B15</f>
-        <v>0</v>
+        <v>1.4425767354267593</v>
       </c>
       <c r="C19" s="11">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.4961529689512301</v>
       </c>
       <c r="D19" s="11">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.9983284690199925</v>
       </c>
       <c r="E19" s="11">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.3707862088742897</v>
       </c>
       <c r="F19" s="11">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.3937644850919386</v>
       </c>
       <c r="G19" s="11">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.5052436280669039</v>
       </c>
       <c r="H19" s="11">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.6703524306153681</v>
       </c>
       <c r="I19" s="11">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.7156825628637424</v>
       </c>
       <c r="J19" s="11">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2.9841679521838831</v>
       </c>
       <c r="K19" s="11">
         <f t="shared" si="4"/>
-        <v>0.26261845756682906</v>
+        <v>2.8982667614357256</v>
       </c>
       <c r="L19" s="11">
         <f t="shared" si="4"/>
-        <v>0.27195945639531216</v>
+        <v>3.2022011885831954</v>
       </c>
       <c r="M19" s="11">
         <f t="shared" si="4"/>
-        <v>0.25670379790447934</v>
+        <v>3.1098477719705651</v>
       </c>
       <c r="N19" s="11">
         <f t="shared" si="4"/>
-        <v>0.27113555290246677</v>
+        <v>3.1227948505688037</v>
       </c>
       <c r="O19" s="11">
         <f t="shared" si="4"/>
-        <v>0.28038724040274238</v>
+        <v>3.211483810780309</v>
       </c>
       <c r="P19" s="11">
         <f t="shared" si="4"/>
-        <v>0.29168095913745068</v>
+        <v>3.1162495634343022</v>
       </c>
       <c r="Q19" s="11">
         <f t="shared" si="4"/>
-        <v>0.35830362174918096</v>
+        <v>3.5521479742375699</v>
       </c>
       <c r="R19" s="11">
         <f t="shared" si="4"/>
-        <v>0.38804641778105581</v>
+        <v>3.6260075104131442</v>
       </c>
       <c r="S19" s="11">
         <f t="shared" si="4"/>
-        <v>0.21924997169207833</v>
+        <v>3.1299179197519704</v>
       </c>
       <c r="T19" s="11" t="e">
         <f t="shared" si="4"/>
@@ -2028,79 +2040,79 @@
     </row>
     <row r="20" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="B20" s="11">
         <f t="shared" ref="B20:AA20" si="5">B14/B21</f>
-        <v>0</v>
+        <v>13.575345236265381</v>
       </c>
       <c r="C20" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>21.309023963356733</v>
       </c>
       <c r="D20" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>12.086700190986209</v>
       </c>
       <c r="E20" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>22.46472927686214</v>
       </c>
       <c r="F20" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>38.311672867148324</v>
       </c>
       <c r="G20" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>51.849494252230436</v>
       </c>
       <c r="H20" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>21.773162190681958</v>
       </c>
       <c r="I20" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>32.908645124312777</v>
       </c>
       <c r="J20" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>47.763506176191122</v>
       </c>
       <c r="K20" s="11">
         <f t="shared" si="5"/>
-        <v>10.239554004146052</v>
+        <v>113.00408698269291</v>
       </c>
       <c r="L20" s="11">
         <f t="shared" si="5"/>
-        <v>3.168444188349441</v>
+        <v>37.307015833802012</v>
       </c>
       <c r="M20" s="11">
         <f t="shared" si="5"/>
-        <v>2.7824497708728808</v>
+        <v>33.708091937887325</v>
       </c>
       <c r="N20" s="11">
         <f t="shared" si="5"/>
-        <v>5.4466829069827316</v>
+        <v>62.731991996362247</v>
       </c>
       <c r="O20" s="11">
         <f t="shared" si="5"/>
-        <v>30.891863630327975</v>
+        <v>353.82751294648784</v>
       </c>
       <c r="P20" s="11">
         <f t="shared" si="5"/>
-        <v>2.6206856985966804</v>
+        <v>27.998778831161115</v>
       </c>
       <c r="Q20" s="11">
         <f t="shared" si="5"/>
-        <v>2.9853851465879844</v>
+        <v>29.596490677380878</v>
       </c>
       <c r="R20" s="11">
         <f t="shared" si="5"/>
-        <v>4.1385293851151168</v>
+        <v>38.671504090419944</v>
       </c>
       <c r="S20" s="11">
         <f t="shared" si="5"/>
-        <v>4.8453501110164412</v>
+        <v>69.170125874595499</v>
       </c>
       <c r="T20" s="11" t="e">
         <f t="shared" si="5"/>
@@ -2137,7 +2149,7 @@
     </row>
     <row r="21" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="B21" s="6">
         <f t="shared" ref="B21:AA21" si="6">B10/B13</f>
@@ -2246,7 +2258,7 @@
     </row>
     <row r="22" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="B22" s="10">
         <f t="shared" ref="B22:AA22" si="7">B7/B9</f>
@@ -2355,165 +2367,65 @@
     </row>
     <row r="23" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K24" s="17">
-        <v>52380933000000</v>
-      </c>
-      <c r="L24" s="17">
-        <v>30932743000000</v>
-      </c>
-      <c r="M24" s="17">
-        <v>5368132000000</v>
-      </c>
-      <c r="N24" s="17">
-        <v>17469626000000</v>
-      </c>
-      <c r="O24" s="17">
-        <v>4832090000000</v>
-      </c>
-      <c r="P24" s="17">
-        <v>34897180000000</v>
-      </c>
-      <c r="Q24" s="17">
-        <v>3708330000000</v>
-      </c>
-      <c r="R24" s="17">
-        <v>39418494000000</v>
-      </c>
-      <c r="S24" s="17">
-        <v>1726556000000</v>
-      </c>
-      <c r="T24" s="17" t="s">
-        <v>71</v>
-      </c>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="17"/>
+      <c r="R24" s="17"/>
+      <c r="S24" s="17"/>
+      <c r="T24" s="17"/>
     </row>
     <row r="25" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K26" s="17">
-        <v>45857963000000</v>
-      </c>
-      <c r="L26" s="17">
-        <v>24630760000000</v>
-      </c>
-      <c r="M26" s="17">
-        <v>4460703000000</v>
-      </c>
-      <c r="N26" s="17">
-        <v>11706869000000</v>
-      </c>
-      <c r="O26" s="17">
-        <v>3480000000000</v>
-      </c>
-      <c r="P26" s="17">
-        <v>34136370000000</v>
-      </c>
-      <c r="Q26" s="17">
-        <v>5643863000000</v>
-      </c>
-      <c r="R26" s="17">
-        <v>70704988000000</v>
-      </c>
-      <c r="S26" s="17">
-        <v>5773901000000</v>
-      </c>
-      <c r="T26" s="17" t="s">
-        <v>71</v>
-      </c>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="17"/>
+      <c r="R26" s="17"/>
+      <c r="S26" s="17"/>
+      <c r="T26" s="17"/>
     </row>
     <row r="27" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K27" s="17">
-        <v>43716001000000</v>
-      </c>
-      <c r="L27" s="17">
-        <v>22325382000000</v>
-      </c>
-      <c r="M27" s="17">
-        <v>4186323000000</v>
-      </c>
-      <c r="N27" s="17">
-        <v>11811932000000</v>
-      </c>
-      <c r="O27" s="17">
-        <v>4250000000000</v>
-      </c>
-      <c r="P27" s="17">
-        <v>31885954000000</v>
-      </c>
-      <c r="Q27" s="17">
-        <v>3365043000000</v>
-      </c>
-      <c r="R27" s="17">
-        <v>50604542000000</v>
-      </c>
-      <c r="S27" s="17">
-        <v>4015120000000</v>
-      </c>
-      <c r="T27" s="17" t="s">
-        <v>71</v>
-      </c>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17"/>
+      <c r="R27" s="17"/>
+      <c r="S27" s="17"/>
+      <c r="T27" s="17"/>
     </row>
     <row r="28" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K28" s="17">
-        <v>43149273000000</v>
-      </c>
-      <c r="L28" s="17">
-        <v>21712537000000</v>
-      </c>
-      <c r="M28" s="17">
-        <v>3381678000000</v>
-      </c>
-      <c r="N28" s="17">
-        <v>12714801000000</v>
-      </c>
-      <c r="O28" s="17">
-        <v>4777353000000</v>
-      </c>
-      <c r="P28" s="17">
-        <v>30415323000000</v>
-      </c>
-      <c r="Q28" s="17">
-        <v>1900390000000</v>
-      </c>
-      <c r="R28" s="17">
-        <v>33061683000000</v>
-      </c>
-      <c r="S28" s="17">
-        <v>2133968000000</v>
-      </c>
-      <c r="T28" s="17" t="s">
-        <v>71</v>
-      </c>
+      <c r="K28" s="17"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="17"/>
+      <c r="T28" s="17"/>
     </row>
     <row r="29" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K29" s="17">
-        <v>43765363000000</v>
-      </c>
-      <c r="L29" s="17">
-        <v>22408711000000</v>
-      </c>
-      <c r="M29" s="17">
-        <v>5773705000000</v>
-      </c>
-      <c r="N29" s="17">
-        <v>11938263000000</v>
-      </c>
-      <c r="O29" s="17">
-        <v>4400000000000</v>
-      </c>
-      <c r="P29" s="17">
-        <v>31810990000000</v>
-      </c>
-      <c r="Q29" s="17">
-        <v>1537031000000</v>
-      </c>
-      <c r="R29" s="17">
-        <v>17704697000000</v>
-      </c>
-      <c r="S29" s="17">
-        <v>2598615000000</v>
-      </c>
-      <c r="T29" s="17" t="s">
-        <v>71</v>
-      </c>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="17"/>
+      <c r="T29" s="17"/>
     </row>
     <row r="30" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="31" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3493,7 +3405,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB258A72-9464-5845-A57C-12441F1547AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -3504,16 +3416,16 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C1" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D1" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -3548,7 +3460,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -3562,142 +3474,142 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="C2" s="1">
         <v>3734</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="C3" s="1">
         <v>6365</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="C4" s="3">
         <v>6267</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="C5" s="3">
         <v>5029</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="C6" s="3">
         <v>10794</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="C7" s="3">
         <v>3356</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="C8" s="3">
         <v>16348</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="C9" s="3">
         <v>1528</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="C10" s="3">
         <v>11009</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/data/ground_truth/CPIN.xlsx
+++ b/data/ground_truth/CPIN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/muhammadnajmirahmani/Belajar/ProjectDatasaur/data/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD0A913-2B62-D143-8B15-C3B28076C4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53FCAEC-B403-3749-9F43-2EF716EF3A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29300" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -362,7 +362,7 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
@@ -1031,7 +1031,7 @@
         <v>4400000000000</v>
       </c>
       <c r="H8" s="18">
-        <v>5400000000000</v>
+        <v>7392848000000</v>
       </c>
       <c r="I8" s="18">
         <v>6575000000000</v>
@@ -1415,13 +1415,13 @@
         <v>40</v>
       </c>
       <c r="B14" s="4">
-        <v>3070</v>
+        <v>3010</v>
       </c>
       <c r="C14" s="4">
         <v>3350</v>
       </c>
       <c r="D14" s="4">
-        <v>4160</v>
+        <v>4200</v>
       </c>
       <c r="E14" s="4">
         <v>4610</v>
@@ -1436,13 +1436,13 @@
         <v>4930</v>
       </c>
       <c r="I14" s="5">
-        <v>4790</v>
+        <v>4760</v>
       </c>
       <c r="J14" s="5">
         <v>5150</v>
       </c>
       <c r="K14" s="5">
-        <v>4900</v>
+        <v>4820</v>
       </c>
       <c r="L14" s="5">
         <v>5275</v>
@@ -1487,7 +1487,7 @@
         <v>6700</v>
       </c>
       <c r="Z14" s="7">
-        <v>6250</v>
+        <v>6375</v>
       </c>
       <c r="AA14" s="7">
         <v>5950</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="B19" s="11">
         <f t="shared" ref="B19:AA19" si="4">B14/B15</f>
-        <v>1.4425767354267593</v>
+        <v>1.414383053301155</v>
       </c>
       <c r="C19" s="11">
         <f t="shared" si="4"/>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="D19" s="11">
         <f t="shared" si="4"/>
-        <v>1.9983284690199925</v>
+        <v>2.0175431658374925</v>
       </c>
       <c r="E19" s="11">
         <f t="shared" si="4"/>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="I19" s="11">
         <f t="shared" si="4"/>
-        <v>2.7156825628637424</v>
+        <v>2.698674112574408</v>
       </c>
       <c r="J19" s="11">
         <f t="shared" si="4"/>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="K19" s="11">
         <f t="shared" si="4"/>
-        <v>2.8982667614357256</v>
+        <v>2.8509481204326934</v>
       </c>
       <c r="L19" s="11">
         <f t="shared" si="4"/>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="B20" s="11">
         <f t="shared" ref="B20:AA20" si="5">B14/B21</f>
-        <v>13.575345236265381</v>
+        <v>13.310029042722736</v>
       </c>
       <c r="C20" s="11">
         <f t="shared" si="5"/>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D20" s="11">
         <f t="shared" si="5"/>
-        <v>12.086700190986209</v>
+        <v>12.202918462053384</v>
       </c>
       <c r="E20" s="11">
         <f t="shared" si="5"/>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="I20" s="11">
         <f t="shared" si="5"/>
-        <v>32.908645124312777</v>
+        <v>32.702536699734623</v>
       </c>
       <c r="J20" s="11">
         <f t="shared" si="5"/>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="K20" s="11">
         <f t="shared" si="5"/>
-        <v>113.00408698269291</v>
+        <v>111.15912229726119</v>
       </c>
       <c r="L20" s="11">
         <f t="shared" si="5"/>
@@ -2392,6 +2392,15 @@
       <c r="T26" s="17"/>
     </row>
     <row r="27" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
       <c r="K27" s="17"/>
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
@@ -2404,6 +2413,15 @@
       <c r="T27" s="17"/>
     </row>
     <row r="28" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
       <c r="K28" s="17"/>
       <c r="L28" s="17"/>
       <c r="M28" s="17"/>
@@ -2416,6 +2434,15 @@
       <c r="T28" s="17"/>
     </row>
     <row r="29" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
       <c r="K29" s="17"/>
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
@@ -2427,41 +2454,396 @@
       <c r="S29" s="17"/>
       <c r="T29" s="17"/>
     </row>
-    <row r="30" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+    </row>
+    <row r="31" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+    </row>
+    <row r="32" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+    </row>
+    <row r="33" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+    </row>
+    <row r="34" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+    </row>
+    <row r="35" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+    </row>
+    <row r="36" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+    </row>
+    <row r="37" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+    </row>
+    <row r="38" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+    </row>
+    <row r="39" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="17"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
+    </row>
+    <row r="40" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="17"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
+    </row>
+    <row r="41" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+    </row>
+    <row r="42" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="J42" s="17"/>
+      <c r="K42" s="17"/>
+    </row>
+    <row r="43" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="17"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="17"/>
+      <c r="K43" s="17"/>
+    </row>
+    <row r="44" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
+    </row>
+    <row r="45" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="17"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="17"/>
+      <c r="M46" s="17"/>
+      <c r="N46" s="17"/>
+      <c r="O46" s="17"/>
+      <c r="P46" s="17"/>
+      <c r="Q46" s="17"/>
+      <c r="R46" s="17"/>
+      <c r="S46" s="17"/>
+    </row>
+    <row r="47" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="17"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="17"/>
+      <c r="I47" s="17"/>
+      <c r="J47" s="17"/>
+      <c r="K47" s="17"/>
+      <c r="L47" s="17"/>
+      <c r="M47" s="17"/>
+      <c r="N47" s="17"/>
+      <c r="O47" s="17"/>
+      <c r="P47" s="17"/>
+      <c r="Q47" s="17"/>
+      <c r="R47" s="17"/>
+      <c r="S47" s="17"/>
+    </row>
+    <row r="48" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="17"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="17"/>
+      <c r="M48" s="17"/>
+      <c r="N48" s="17"/>
+      <c r="O48" s="17"/>
+      <c r="P48" s="17"/>
+      <c r="Q48" s="17"/>
+      <c r="R48" s="17"/>
+      <c r="S48" s="17"/>
+    </row>
+    <row r="49" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="17"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="17"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="17"/>
+      <c r="I49" s="17"/>
+      <c r="J49" s="17"/>
+      <c r="K49" s="17"/>
+      <c r="L49" s="17"/>
+      <c r="M49" s="17"/>
+      <c r="N49" s="17"/>
+      <c r="O49" s="17"/>
+      <c r="P49" s="17"/>
+      <c r="Q49" s="17"/>
+      <c r="R49" s="17"/>
+      <c r="S49" s="17"/>
+    </row>
+    <row r="50" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="17"/>
+      <c r="G50" s="17"/>
+      <c r="H50" s="17"/>
+      <c r="I50" s="17"/>
+      <c r="J50" s="17"/>
+      <c r="K50" s="17"/>
+      <c r="L50" s="17"/>
+      <c r="M50" s="17"/>
+      <c r="N50" s="17"/>
+      <c r="O50" s="17"/>
+      <c r="P50" s="17"/>
+      <c r="Q50" s="17"/>
+      <c r="R50" s="17"/>
+      <c r="S50" s="17"/>
+    </row>
+    <row r="51" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="17"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
+      <c r="F51" s="17"/>
+      <c r="G51" s="17"/>
+      <c r="H51" s="17"/>
+      <c r="I51" s="17"/>
+      <c r="J51" s="17"/>
+      <c r="K51" s="17"/>
+      <c r="L51" s="17"/>
+      <c r="M51" s="17"/>
+      <c r="N51" s="17"/>
+      <c r="O51" s="17"/>
+      <c r="P51" s="17"/>
+      <c r="Q51" s="17"/>
+      <c r="R51" s="17"/>
+      <c r="S51" s="17"/>
+    </row>
+    <row r="52" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B52" s="17"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="17"/>
+      <c r="H52" s="17"/>
+      <c r="I52" s="17"/>
+      <c r="J52" s="17"/>
+      <c r="K52" s="17"/>
+      <c r="L52" s="17"/>
+      <c r="M52" s="17"/>
+      <c r="N52" s="17"/>
+      <c r="O52" s="17"/>
+      <c r="P52" s="17"/>
+      <c r="Q52" s="17"/>
+      <c r="R52" s="17"/>
+      <c r="S52" s="17"/>
+    </row>
+    <row r="53" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="17"/>
+      <c r="C53" s="17"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="17"/>
+      <c r="H53" s="17"/>
+      <c r="I53" s="17"/>
+      <c r="J53" s="17"/>
+      <c r="K53" s="17"/>
+      <c r="L53" s="17"/>
+      <c r="M53" s="17"/>
+      <c r="N53" s="17"/>
+      <c r="O53" s="17"/>
+      <c r="P53" s="17"/>
+      <c r="Q53" s="17"/>
+      <c r="R53" s="17"/>
+      <c r="S53" s="17"/>
+    </row>
+    <row r="54" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="17"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="17"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="17"/>
+      <c r="I54" s="17"/>
+      <c r="J54" s="17"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="17"/>
+      <c r="M54" s="17"/>
+      <c r="N54" s="17"/>
+      <c r="O54" s="17"/>
+      <c r="P54" s="17"/>
+      <c r="Q54" s="17"/>
+      <c r="R54" s="17"/>
+      <c r="S54" s="17"/>
+    </row>
+    <row r="55" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="17"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
+      <c r="F55" s="17"/>
+      <c r="G55" s="17"/>
+      <c r="H55" s="17"/>
+      <c r="I55" s="17"/>
+      <c r="J55" s="17"/>
+      <c r="K55" s="17"/>
+      <c r="L55" s="17"/>
+      <c r="M55" s="17"/>
+      <c r="N55" s="17"/>
+      <c r="O55" s="17"/>
+      <c r="P55" s="17"/>
+      <c r="Q55" s="17"/>
+      <c r="R55" s="17"/>
+      <c r="S55" s="17"/>
+    </row>
+    <row r="56" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
